--- a/artfynd/A 72945-2021 artfynd.xlsx
+++ b/artfynd/A 72945-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 72945-2021 artfynd.xlsx
+++ b/artfynd/A 72945-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>98376192</v>
       </c>
       <c r="B2" t="n">
-        <v>89652</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>578573.1630676701</v>
+        <v>578573</v>
       </c>
       <c r="R2" t="n">
-        <v>6413705.648352366</v>
+        <v>6413706</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,19 +754,9 @@
           <t>2022-01-27</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-01-27</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -807,12 +792,7 @@
         <v>98376203</v>
       </c>
       <c r="B3" t="n">
-        <v>89376</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -851,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>578573.1630676701</v>
+        <v>578573</v>
       </c>
       <c r="R3" t="n">
-        <v>6413705.648352366</v>
+        <v>6413706</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -884,19 +864,9 @@
           <t>2022-01-27</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-01-27</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
